--- a/construtoras_leads_report.xlsx
+++ b/construtoras_leads_report.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>06 May 2026 18:26</t>
+          <t>08 May 2026 17:52</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Ranked by enriched Lead Score v3.0 · 06 May 2026</t>
+          <t>Ranked by enriched Lead Score v3.0 · 08 May 2026</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="Y5" s="17" t="inlineStr">
         <is>
-          <t>Direcional (DIRR3), MRV (MRVE3), Cury (CURY3): o que esperar das construtoras no 1T26, segundo o Santander (Seu Dinheiro, 2026-05-05) | O grande teste das incorporadoras: quem aguenta mais um ano de crédito caro no setor? Itaú BBA responde (Seu Dinheiro, 2026-04-23) | Direcional Engenharia registra maior VGV de lançamentos da história, com R$ 1,9 bi no segundo trimestre (Diário do Comércio, 2025-08-12)</t>
+          <t>Direcional Engenharia registra maior VGV de lançamentos da história, com R$ 1,9 bi no segundo trimestre (Diário do Comércio, 2025-08-12) | Direcional Engenharia paga comissões com a Split C (Baguete, 2025-11-07) | Programa de estágio: Direcional Engenharia e Rive Incorporadora abrem vagas (IstoÉ Dinheiro, 2022-05-12)</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="Y6" s="26" t="inlineStr">
         <is>
-          <t>5 melhores construtoras do Minha Casa, Minha Vida! (MANAUSonline.com, 2026-04-23) | Arapongas anuncia novo residencial com 665 novas moradias na Zona Sul (Tribuna do Norte, 2026-04-30)</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Y10" s="26" t="inlineStr">
         <is>
-          <t>Insider-Favored Growth Companies To Watch In June 2024 (Simply Wall St.· via Yahoo Finance, 2024-05-06) | Three Growth Companies With High Insider Ownership And Up To 60% Earnings Growth (Simply Wall St.· via Yahoo Finance, 2024-05-06)</t>
+          <t>Insider-Favored Growth Companies To Watch In June 2024 (Simply Wall St.· via Yahoo Finance, 2024-05-08) | Three Growth Companies With High Insider Ownership And Up To 60% Earnings Growth (Simply Wall St.· via Yahoo Finance, 2024-05-08)</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="Y11" s="26" t="inlineStr">
         <is>
-          <t>Lucro da Tenda dobra no 1º tri e supera estimativas (Terra, 2026-05-05) | Tenda: Lucro líquido consolidado atinge R$ 183,4 milhões no primeiro trimestre (O POVO, 2026-05-05)</t>
+          <t>Tenda (TEND3): lucro dobra no 1º tri, vai a R$ 183,4 milhões e supera estimativas (InfoMoney, 2026-05-05) | Tenda: Lucro líquido consolidado atinge R$ 183,4 milhões no primeiro trimestre (O POVO, 2026-05-06) | Lucro da Tenda dobra no 1º tri e supera estimativas (Terra, 2026-05-05)</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="Y13" s="26" t="inlineStr">
         <is>
-          <t>Direcional (DIRR3), MRV (MRVE3), Cury (CURY3): o que esperar das construtoras no 1T26, segundo o Santander (Seu Dinheiro, 2026-05-05) | Por que as construtoras despencaram na bolsa hoje? Entenda (Valor Investe, 2026-04-27) | Desempenho desigual: O que esperar das construtoras no 1T26, segundo o Santander (Money Times, 2026-05-05)</t>
+          <t>Direcional (DIRR3), MRV (MRVE3), Cury (CURY3): o que esperar das construtoras no 1T26, segundo o Santander (Seu Dinheiro, 2026-05-05) | Alta de custos é grande vilã de construtoras na B3 – mas analistas veem oportunidades (InfoMoney, 2026-05-07) | Por que as construtoras despencaram na bolsa hoje? Entenda (Valor Investe, 2026-04-27)</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="V15" s="19" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>416</t>
         </is>
       </c>
       <c r="W15" s="19" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="Y15" s="26" t="inlineStr">
         <is>
-          <t>Trisa Incorporadora: Natureza e sofisticação no Agreste (Folha PE, 2026-04-22) | PDG, Gafisa, Alphaville: incorporadoras em crise lutam para recuperar confiança de investidores (Estadão, 2026-04-24) | Expansão do MCMV estimula incorporadoras a retomar lançamentos para classe média (Estadão, 2026-04-25)</t>
+          <t>PDG, Gafisa, Alphaville: incorporadoras em crise lutam para recuperar confiança de investidores (Estadão, 2026-04-24) | Incorporadora boutique: especialização que agrega valor (g1, 2026-05-01) | Incorporadora antecipa decorado em projeto de alto padrão em Curitiba (g1, 2026-04-28)</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="V19" s="19" t="inlineStr">
         <is>
-          <t>8.1K</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="W19" s="19" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AA2" s="19" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="AB2" s="19" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AI2" s="26" t="inlineStr">
         <is>
-          <t>Direcional (DIRR3), MRV (MRVE3), Cury (CURY3): o que esperar das construtoras no 1T26, segundo o Santander (Seu Dinheiro, 2026-05-05) | O grande teste das incorporadoras: quem aguenta mais um ano de crédito caro no setor? Itaú BBA responde (Seu Dinheiro, 2026-04-23) | Direcional Engenharia registra maior VGV de lançamentos da história, com R$ 1,9 bi no segundo trimestre (Diário do Comércio, 2025-08-12)</t>
+          <t>Direcional Engenharia registra maior VGV de lançamentos da história, com R$ 1,9 bi no segundo trimestre (Diário do Comércio, 2025-08-12) | Direcional Engenharia paga comissões com a Split C (Baguete, 2025-11-07) | Programa de estágio: Direcional Engenharia e Rive Incorporadora abrem vagas (IstoÉ Dinheiro, 2022-05-12)</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="AI3" s="26" t="inlineStr">
         <is>
-          <t>5 melhores construtoras do Minha Casa, Minha Vida! (MANAUSonline.com, 2026-04-23) | Arapongas anuncia novo residencial com 665 novas moradias na Zona Sul (Tribuna do Norte, 2026-04-30)</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AA4" s="19" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="AB4" s="19" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="AA5" s="19" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AB5" s="19" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AA6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AB6" s="19" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AI7" s="26" t="inlineStr">
         <is>
-          <t>Insider-Favored Growth Companies To Watch In June 2024 (Simply Wall St.· via Yahoo Finance, 2024-05-06) | Three Growth Companies With High Insider Ownership And Up To 60% Earnings Growth (Simply Wall St.· via Yahoo Finance, 2024-05-06)</t>
+          <t>Insider-Favored Growth Companies To Watch In June 2024 (Simply Wall St.· via Yahoo Finance, 2024-05-08) | Three Growth Companies With High Insider Ownership And Up To 60% Earnings Growth (Simply Wall St.· via Yahoo Finance, 2024-05-08)</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="AA8" s="19" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AB8" s="19" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI8" s="26" t="inlineStr">
         <is>
-          <t>Lucro da Tenda dobra no 1º tri e supera estimativas (Terra, 2026-05-05) | Tenda: Lucro líquido consolidado atinge R$ 183,4 milhões no primeiro trimestre (O POVO, 2026-05-05)</t>
+          <t>Tenda (TEND3): lucro dobra no 1º tri, vai a R$ 183,4 milhões e supera estimativas (InfoMoney, 2026-05-05) | Tenda: Lucro líquido consolidado atinge R$ 183,4 milhões no primeiro trimestre (O POVO, 2026-05-06) | Lucro da Tenda dobra no 1º tri e supera estimativas (Terra, 2026-05-05)</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AA9" s="19" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AB9" s="19" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="AA10" s="19" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AB10" s="19" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AI10" s="26" t="inlineStr">
         <is>
-          <t>Direcional (DIRR3), MRV (MRVE3), Cury (CURY3): o que esperar das construtoras no 1T26, segundo o Santander (Seu Dinheiro, 2026-05-05) | Por que as construtoras despencaram na bolsa hoje? Entenda (Valor Investe, 2026-04-27) | Desempenho desigual: O que esperar das construtoras no 1T26, segundo o Santander (Money Times, 2026-05-05)</t>
+          <t>Direcional (DIRR3), MRV (MRVE3), Cury (CURY3): o que esperar das construtoras no 1T26, segundo o Santander (Seu Dinheiro, 2026-05-05) | Alta de custos é grande vilã de construtoras na B3 – mas analistas veem oportunidades (InfoMoney, 2026-05-07) | Por que as construtoras despencaram na bolsa hoje? Entenda (Valor Investe, 2026-04-27)</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AA11" s="19" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AB11" s="19" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="Z12" s="19" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>416</t>
         </is>
       </c>
       <c r="AA12" s="19" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="AI12" s="26" t="inlineStr">
         <is>
-          <t>Trisa Incorporadora: Natureza e sofisticação no Agreste (Folha PE, 2026-04-22) | PDG, Gafisa, Alphaville: incorporadoras em crise lutam para recuperar confiança de investidores (Estadão, 2026-04-24) | Expansão do MCMV estimula incorporadoras a retomar lançamentos para classe média (Estadão, 2026-04-25)</t>
+          <t>PDG, Gafisa, Alphaville: incorporadoras em crise lutam para recuperar confiança de investidores (Estadão, 2026-04-24) | Incorporadora boutique: especialização que agrega valor (g1, 2026-05-01) | Incorporadora antecipa decorado em projeto de alto padrão em Curitiba (g1, 2026-04-28)</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="AA13" s="19" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AB13" s="19" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="AA15" s="19" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="AB15" s="19" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="Z16" s="19" t="inlineStr">
         <is>
-          <t>8.1K</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AA16" s="19" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AB16" s="19" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AA18" s="28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AB18" s="28" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AA19" s="28" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AB19" s="28" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AA20" s="28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>119</t>
         </is>
       </c>
       <c r="AB20" s="28" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AA21" s="28" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="AB21" s="28" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="AA23" s="28" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="AB23" s="28" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="AI23" s="34" t="inlineStr">
         <is>
-          <t>5 melhores construtoras do Minha Casa, Minha Vida! (MANAUSonline.com, 2026-04-23) | Incorporadora antecipa decorado em projeto de alto padrão em Curitiba (g1, 2026-04-28) | Construtora deve devolver valor integral do imóvel se entrega atrasar mais de 180 dias (Consultor Jurídico, 2026-04-23)</t>
+          <t>Empar lança loteamento em Praia Grande, impulsionado pelo crescimento de Aracruz (A Gazeta, 2026-04-30)</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="AA25" s="28" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="AB25" s="28" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="AA28" s="28" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="AB28" s="28" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="AI28" s="34" t="inlineStr">
         <is>
-          <t>Empar lança loteamento em Praia Grande, impulsionado pelo crescimento de Aracruz (A Gazeta, 2026-04-30) | Impulsionada por Aracruz, Praia Grande ganha novo loteamento com foco em valorização (A Gazeta, 2026-05-01) | Housi mira R$ 6 bilhões em lançamentos em nova vertical voltada para saúde (Exame, 2026-04-25)</t>
+          <t>Housi mira R$ 6 bilhões em lançamentos em nova vertical voltada para saúde (Exame, 2026-04-25)</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AA29" s="28" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AB29" s="28" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AA33" s="28" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>687</t>
         </is>
       </c>
       <c r="AB33" s="28" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="AA35" s="28" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AB35" s="28" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AA36" s="28" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AB36" s="28" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="Z37" s="28" t="inlineStr">
         <is>
-          <t>7.7K</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AA37" s="28" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AB37" s="28" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="Z39" s="28" t="inlineStr">
         <is>
-          <t>5.7K</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AA39" s="28" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AB39" s="28" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="AA40" s="28" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AB40" s="28" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="AI40" s="34" t="inlineStr">
         <is>
-          <t>5 melhores construtoras do Minha Casa, Minha Vida! (MANAUSonline.com, 2026-04-23)</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="AA42" s="28" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>916</t>
         </is>
       </c>
       <c r="AB42" s="28" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AA43" s="28" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="AB43" s="28" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="AA44" s="28" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="AB44" s="28" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="AA45" s="28" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AB45" s="28" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="Z46" s="37" t="inlineStr">
         <is>
-          <t>8.4K</t>
+          <t>8.5K</t>
         </is>
       </c>
       <c r="AA46" s="37" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="AB46" s="37" t="inlineStr">
@@ -12075,12 +12075,12 @@
       </c>
       <c r="Z48" s="37" t="inlineStr">
         <is>
-          <t>6.5K</t>
+          <t>6.4K</t>
         </is>
       </c>
       <c r="AA48" s="37" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="AB48" s="37" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="AA49" s="45" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="AB49" s="45" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="AA50" s="37" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="AB50" s="37" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="AA52" s="37" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="AB52" s="37" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AA53" s="45" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>976</t>
         </is>
       </c>
       <c r="AB53" s="45" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="AA54" s="37" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="AB54" s="37" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="AA55" s="45" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>790</t>
         </is>
       </c>
       <c r="AB55" s="45" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="AI55" s="51" t="inlineStr">
         <is>
-          <t>O grande teste das incorporadoras: quem aguenta mais um ano de crédito caro no setor? Itaú BBA responde (Seu Dinheiro, 2026-04-23)</t>
+          <t>Expansão do MCMV estimula incorporadoras a retomar lançamentos para classe média (Estadão, 2026-04-25) | Marquise Incorporações cria The Dream Brokers para corretores (Diário do Nordeste, 2026-05-06) | Empresário é acusado de golpe milionário em Arapiraca (TribunaHoje.com, 2026-04-25)</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="AA56" s="37" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>595</t>
         </is>
       </c>
       <c r="AB56" s="37" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="AA57" s="45" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>926</t>
         </is>
       </c>
       <c r="AB57" s="45" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AA58" s="37" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AB58" s="37" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="AI59" s="51" t="inlineStr">
         <is>
-          <t>Por que as construtoras despencaram na bolsa hoje? Entenda (Valor Investe, 2026-04-27) | O grande teste das incorporadoras: quem aguenta mais um ano de crédito caro no setor? Itaú BBA responde (Seu Dinheiro, 2026-04-23) | A imobiliária e os danos causados por construtoras (Diário do Comércio, 2026-04-24)</t>
+          <t>Expansão do MCMV estimula incorporadoras a retomar lançamentos para classe média (Estadão, 2026-04-25) | TCE cobra R$ 16,5 mi por rompimento de reservatório que inundou bairro em Florianópolis (ND Mais, 2026-05-05) | Lago Corumbá IV recebe lançamento do Grupo CPR e reorganiza alto padrão de condomínio no Centro-Oeste (O GLOBO, 2026-05-01)</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="AI60" s="43" t="inlineStr">
         <is>
-          <t>Impulsionada por Aracruz, Praia Grande ganha novo loteamento com foco em valorização (A Gazeta, 2026-05-01) | De corretor a 'guru do retrofit': ele mudou o Centro de Porto Alegre ao reformar prédios abandonados (Exame, 2026-04-27) | Artista do MoMa assina obra em prédio de luxo nos Jardins, em São Paulo (Exame, 2026-04-26)</t>
+          <t>Artista do MoMa assina obra em prédio de luxo nos Jardins, em São Paulo (Exame, 2026-04-26)</t>
         </is>
       </c>
     </row>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="AA61" s="45" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>159</t>
         </is>
       </c>
       <c r="AB61" s="45" t="inlineStr">
